--- a/SampleChecklist.xlsx
+++ b/SampleChecklist.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sections" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +531,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Install counterweight safety gear and certify per EN81-20 §5.6.</t>
+          <t>Install counterweight safety gear and certify per EN81-20.</t>
         </is>
       </c>
     </row>
@@ -568,71 +570,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PitToEarth: FALSE AND MaxFFLInt: &gt;11m</t>
+          <t>BuildingClass: "Class 9b" OR MaxFFLInt: &gt;=20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Combined pit + travel safety review</t>
+          <t>Enhanced fire service controls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN81-20</t>
+          <t>BCA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Applies only when both conditions hold.</t>
+          <t>High-rise or assembly buildings need fire service lift controls.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Perform a combined structural and travel safety assessment.</t>
+          <t>Provide fire service control switch and compliant signage.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A13</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BuildingClass: "Class 9b" OR MaxFFLInt: &gt;=20</t>
-        </is>
-      </c>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Enhanced fire service controls</t>
+          <t>Pit structure designed for buffer impact loads</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BCA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>High-rise or assembly buildings need fire service lift controls.</t>
-        </is>
-      </c>
+          <t>AS1170</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Provide fire service control switch and compliant signage.</t>
+          <t>Confirm structural design accounts for buffer reaction forces.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,22 +636,78 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide accessible lift signage on every floor</t>
+          <t>Guide rail bracket spacing verified for travel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>EN81-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Applies to taller installations.</t>
+          <t>Taller installations need verified bracket spacing.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Install tactile/braille floor indicators at each landing.</t>
+          <t>Document guide-rail bracket spacing calculations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Machine room power isolation provided</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AS3000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Install a lockable main switch for the lift supply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PitToEarth: FALSE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Earthing of car and well per wiring rules</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AS3000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Earthing continuity required where pit is not to solid earth.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Measure and record earth continuity resistance.</t>
         </is>
       </c>
     </row>
@@ -814,4 +864,176 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Prefix</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Architectural</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AS3000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AS/NZS 3000 Wiring Rules — electrical installations standard. (sample text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AS1170</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AS/NZS 1170 Structural design actions. (sample text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EN81-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EN 81-20 — safety rules for the construction and installation of lifts. (sample text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BCA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Building Code of Australia. (sample text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DDA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Disability Discrimination Act — accessibility requirements. (sample text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>State/local regulatory requirement. (sample text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RDM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Reference Design Manual. (sample text)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SampleChecklist.xlsx
+++ b/SampleChecklist.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,11 @@
           <t>Example</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Example Image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,6 +483,11 @@
           <t>Fit IP-rated enclosures and weather seals to the landing door head.</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>a08-weather-seal.svg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +512,7 @@
           <t>Provide a protected lobby between the lift and the dwelling entrance.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,6 +545,11 @@
           <t>Install counterweight safety gear and certify per EN81-20.</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>a10-cwt-safety.svg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,6 +582,7 @@
           <t>Add emergency doors at max 11 m spacing along the well.</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -598,6 +615,7 @@
           <t>Provide fire service control switch and compliant signage.</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,6 +640,7 @@
           <t>Confirm structural design accounts for buffer reaction forces.</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -654,6 +673,7 @@
           <t>Document guide-rail bracket spacing calculations.</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -678,6 +698,7 @@
           <t>Install a lockable main switch for the lift supply.</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -710,6 +731,7 @@
           <t>Measure and record earth continuity resistance.</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SampleChecklist.xlsx
+++ b/SampleChecklist.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>a08-weather-seal.svg</t>
+          <t>a08-weather-seal.png</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>a10-cwt-safety.svg</t>
+          <t>a10-cwt-safety.png</t>
         </is>
       </c>
     </row>

--- a/SampleChecklist.xlsx
+++ b/SampleChecklist.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,11 +450,6 @@
           <t>Example</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Example Image</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,11 +475,6 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fit IP-rated enclosures and weather seals to the landing door head.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>a08-weather-seal.png</t>
         </is>
       </c>
@@ -512,7 +502,6 @@
           <t>Provide a protected lobby between the lift and the dwelling entrance.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,11 +531,6 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Install counterweight safety gear and certify per EN81-20.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>a10-cwt-safety.png</t>
         </is>
       </c>
@@ -582,7 +566,6 @@
           <t>Add emergency doors at max 11 m spacing along the well.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +598,6 @@
           <t>Provide fire service control switch and compliant signage.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,7 +622,6 @@
           <t>Confirm structural design accounts for buffer reaction forces.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -673,7 +654,6 @@
           <t>Document guide-rail bracket spacing calculations.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -698,7 +678,6 @@
           <t>Install a lockable main switch for the lift supply.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -731,7 +710,6 @@
           <t>Measure and record earth continuity resistance.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SampleChecklist.xlsx
+++ b/SampleChecklist.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,11 @@
           <t>Example</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,6 +483,11 @@
           <t>a08-weather-seal.png</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://example.com/examples/a08-weather-seal.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,6 +512,7 @@
           <t>Provide a protected lobby between the lift and the dwelling entrance.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,6 +545,11 @@
           <t>a10-cwt-safety.png</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://example.com/examples/a10-cwt-safety.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,6 +582,7 @@
           <t>Add emergency doors at max 11 m spacing along the well.</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -598,6 +615,7 @@
           <t>Provide fire service control switch and compliant signage.</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,6 +640,7 @@
           <t>Confirm structural design accounts for buffer reaction forces.</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -654,6 +673,7 @@
           <t>Document guide-rail bracket spacing calculations.</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -678,6 +698,7 @@
           <t>Install a lockable main switch for the lift supply.</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -710,6 +731,7 @@
           <t>Measure and record earth continuity resistance.</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
